--- a/docs/analysis/extension-usecases/EU_예약상태관리.xlsx
+++ b/docs/analysis/extension-usecases/EU_예약상태관리.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wonsik/Documents/3_1_season/소프트웨어공학/sw-project/ExtendUsecase/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KANG\Desktop\sw-project-v1\ExtendUsecase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52A2208-77EC-6041-BEC8-21BFBABBA0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A2881C-E618-425B-BCA9-19C4C5054B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="17460" windowHeight="20000" xr2:uid="{D4D1709D-9A77-9244-A80B-853B57F4CE38}"/>
+    <workbookView xWindow="8085" yWindow="660" windowWidth="15195" windowHeight="14895" xr2:uid="{D4D1709D-9A77-9244-A80B-853B57F4CE38}"/>
   </bookViews>
   <sheets>
     <sheet name="SFR-400" sheetId="3" r:id="rId1"/>
@@ -83,10 +83,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SFR-401, SFR-402, SFR-403, SFR-404, SFR-405, SFR-406, SFR-407</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>관련 요구사항</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -104,10 +100,6 @@
   </si>
   <si>
     <t>Use Case 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SFR-400</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -242,12 +234,20 @@
     <t>시스템은 예약 상태를 '거부'로 갱신하고, 거절 사유와 함께 저장한다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>SFR-500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFR-501, SFR-502, SFR-503, SFR-504, SFR-505, SFR-506, SFR-507</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -443,6 +443,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -459,15 +477,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -478,15 +487,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,100 +823,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14D9D82-6B09-7741-AF0B-BB26E15DFAB1}">
   <dimension ref="B2:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="5" width="36.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="5" width="36.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" customHeight="1">
+    <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="2:6" ht="18" customHeight="1">
+        <v>15</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
+    </row>
+    <row r="3" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20"/>
-    </row>
-    <row r="4" spans="2:6" ht="18" customHeight="1">
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-    </row>
-    <row r="5" spans="2:6" s="5" customFormat="1" ht="37" customHeight="1">
+      <c r="C4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" spans="2:6" s="5" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-    </row>
-    <row r="6" spans="2:6" ht="18" customHeight="1">
+      <c r="C5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="7" spans="2:6" ht="18" customHeight="1">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
-    </row>
-    <row r="8" spans="2:6" ht="35" customHeight="1">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="25" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="16" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -929,165 +929,165 @@
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="57">
-      <c r="B11" s="26"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="51.75" x14ac:dyDescent="0.3">
+      <c r="B11" s="17"/>
       <c r="C11" s="3">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="2:6" ht="19">
-      <c r="B12" s="26"/>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="17"/>
       <c r="C12" s="3">
         <v>2</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:6" ht="19">
-      <c r="B13" s="26"/>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="17"/>
       <c r="C13" s="3">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="2:6" ht="38">
-      <c r="B14" s="26"/>
+    <row r="14" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="17"/>
       <c r="C14" s="3">
         <v>4</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="2:6" ht="19">
-      <c r="B15" s="26"/>
+    <row r="15" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="17"/>
       <c r="C15" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="2:6" ht="19">
-      <c r="B16" s="26"/>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="17"/>
       <c r="C16" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="2:6" ht="38">
-      <c r="B17" s="26"/>
+    <row r="17" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="17"/>
       <c r="C17" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="2:6" ht="38">
-      <c r="B18" s="26"/>
+    <row r="18" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="17"/>
       <c r="C18" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="2:6" ht="19">
-      <c r="B19" s="26"/>
+    <row r="19" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="17"/>
       <c r="C19" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="2:6" ht="38">
-      <c r="B20" s="26"/>
+    <row r="20" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="17"/>
       <c r="C20" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="2:6" ht="19">
-      <c r="B21" s="26"/>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="17"/>
       <c r="C21" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="2:6" ht="38">
-      <c r="B22" s="26"/>
+    <row r="22" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="17"/>
       <c r="C22" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="2:6" ht="38">
-      <c r="B23" s="26"/>
+    <row r="23" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="17"/>
       <c r="C23" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:6" ht="38">
-      <c r="B24" s="26"/>
+    <row r="24" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="17"/>
       <c r="C24" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="26"/>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="17"/>
       <c r="C25" s="3">
         <v>6</v>
       </c>
@@ -1095,8 +1095,8 @@
       <c r="E25" s="1"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="27"/>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="18"/>
       <c r="C26" s="3">
         <v>7</v>
       </c>
@@ -1104,79 +1104,74 @@
       <c r="E26" s="1"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="2:6" ht="18" customHeight="1">
-      <c r="B27" s="13" t="s">
+    <row r="27" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="17"/>
+      <c r="C27" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="22"/>
+      <c r="E27" s="23"/>
       <c r="F27" s="11"/>
     </row>
-    <row r="28" spans="2:6" ht="19">
-      <c r="B28" s="14"/>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="20"/>
       <c r="C28" s="12">
         <v>1</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="2:6" ht="19">
-      <c r="B29" s="24"/>
+    <row r="29" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B29" s="27"/>
       <c r="C29" s="12">
         <v>2</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="13" t="s">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="17"/>
+      <c r="C30" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="23"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="2:6" ht="38">
-      <c r="B31" s="14"/>
+    <row r="31" spans="2:6" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B31" s="20"/>
       <c r="C31" s="3">
         <v>1</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="2:6" ht="19">
-      <c r="B32" s="14"/>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="20"/>
       <c r="C32" s="3">
         <v>2</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F32" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B10:B26"/>
     <mergeCell ref="B30:B32"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C30:E30"/>
@@ -1185,6 +1180,11 @@
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B10:B26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
